--- a/24_DS_Gen_Ahm_1/Advanced Excel/Oct15.xlsx
+++ b/24_DS_Gen_Ahm_1/Advanced Excel/Oct15.xlsx
@@ -5,18 +5,19 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\Batches\24_DS_Gen_Ahm_1\Advanced Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\24_DS_Gen_Ahm_1\Advanced Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B61BC860-6695-4851-83F4-8841F4A88604}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB3866EC-D43C-4E0E-95CA-B0E42A8C8877}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datefunc" sheetId="2" r:id="rId1"/>
     <sheet name="Data Validation" sheetId="3" r:id="rId2"/>
     <sheet name="Population" sheetId="4" r:id="rId3"/>
     <sheet name="Per Capita Income" sheetId="5" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="74">
   <si>
     <t>Which rows have April as their month and 'Numbers' at least 10?</t>
   </si>
@@ -217,16 +218,49 @@
   </si>
   <si>
     <t>STD Code (Can't find using VLOOKUP!)</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>SR Tendulkar</t>
+  </si>
+  <si>
+    <t>V Sehwag</t>
+  </si>
+  <si>
+    <t>V Kohli</t>
+  </si>
+  <si>
+    <t>Matches</t>
+  </si>
+  <si>
+    <t>100's</t>
+  </si>
+  <si>
+    <t>50's</t>
+  </si>
+  <si>
+    <t>6's</t>
+  </si>
+  <si>
+    <t>4s</t>
+  </si>
+  <si>
+    <t>Player Name</t>
+  </si>
+  <si>
+    <t>Row Number of the Parameter</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-14009]dd\-mm\-yyyy;@"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -247,6 +281,19 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">
@@ -322,7 +369,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -341,12 +388,45 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <dxfs count="3">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9E2F3"/>
+          <bgColor rgb="FFD9E2F3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9E2F3"/>
+          <bgColor rgb="FFD9E2F3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
+  <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="Question Hlookup unworked-style" pivot="0" count="3" xr9:uid="{0DE1BC27-DED7-4FF2-984E-5ABE63FC3B8D}">
+      <tableStyleElement type="headerRow" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="secondRowStripe" dxfId="0"/>
+    </tableStyle>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -356,6 +436,18 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{66856DA5-52E8-423E-B4F9-D94FD14BA903}" name="Table_56" displayName="Table_56" ref="B2:E7">
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{7CD4923C-8CE7-4910-B462-D3C37C419A08}" name="Name"/>
+    <tableColumn id="2" xr3:uid="{2F914BEB-B1EA-4680-8668-63DD6E99B70A}" name="SR Tendulkar"/>
+    <tableColumn id="3" xr3:uid="{89DDA7BC-7CDB-4B60-A4DF-863F96AD1188}" name="V Sehwag"/>
+    <tableColumn id="4" xr3:uid="{AD26C33B-08E3-45FA-B5DC-A101E8795176}" name="V Kohli"/>
+  </tableColumns>
+  <tableStyleInfo name="Question Hlookup unworked-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2585,4 +2677,143 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCA5DC72-07E5-4CAB-980D-8A1D9FC4AC58}">
+  <dimension ref="B2:K7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="26.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B2" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="G2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B3" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="C3" s="15">
+        <v>200</v>
+      </c>
+      <c r="D3" s="15">
+        <v>97</v>
+      </c>
+      <c r="E3" s="15">
+        <v>98</v>
+      </c>
+      <c r="G3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H3" t="s">
+        <v>70</v>
+      </c>
+      <c r="J3" t="s">
+        <v>73</v>
+      </c>
+      <c r="K3">
+        <f>MATCH(H3, Table_56[[#All],[Name]], 0)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B4" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="C4" s="15">
+        <v>20</v>
+      </c>
+      <c r="D4" s="15">
+        <v>22</v>
+      </c>
+      <c r="E4" s="15">
+        <v>21</v>
+      </c>
+      <c r="G4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H4">
+        <f>HLOOKUP(H2, Table_56[[#All],[SR Tendulkar]:[V Kohli]], K3, FALSE)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B5" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="C5" s="15">
+        <v>32</v>
+      </c>
+      <c r="D5" s="15">
+        <v>35</v>
+      </c>
+      <c r="E5" s="15">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B6" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="C6" s="15">
+        <v>100</v>
+      </c>
+      <c r="D6" s="15">
+        <v>25</v>
+      </c>
+      <c r="E6" s="15">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B7" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="C7" s="15">
+        <v>125</v>
+      </c>
+      <c r="D7" s="15">
+        <v>20</v>
+      </c>
+      <c r="E7" s="15">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2" xr:uid="{0356D147-7B65-4700-B3FE-138994E463D8}">
+      <formula1>$C$2:$E$2</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3" xr:uid="{4DAFDE24-F33B-4D15-8593-AC737B34D23B}">
+      <formula1>$B$3:$B$7</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>